--- a/docs/resources/Dictionary_testCohort.xlsx
+++ b/docs/resources/Dictionary_testCohort.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brend\Molgenis\repos\molgenis-emx2\docs\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68382FD5-1C08-4890-A470-4DF7709A8429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C978146-3D7B-435B-9739-4D9C2F78E862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="11985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datasets" sheetId="9" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="143">
   <si>
     <t>label</t>
   </si>
@@ -378,9 +378,6 @@
     <t>family_disease</t>
   </si>
   <si>
-    <t>disease</t>
-  </si>
-  <si>
     <t>Family disease on mother's side</t>
   </si>
   <si>
@@ -421,6 +418,39 @@
   </si>
   <si>
     <t>variable</t>
+  </si>
+  <si>
+    <t>original language description</t>
+  </si>
+  <si>
+    <t>Woont de partner bij de moeder in huis?</t>
+  </si>
+  <si>
+    <t>Apgar score 5 minuten na geboorte van het kind</t>
+  </si>
+  <si>
+    <t>Geboortegewicht</t>
+  </si>
+  <si>
+    <t>Lengte bij geboorte</t>
+  </si>
+  <si>
+    <t>Gewicht van het kind bij aangegeven leeftijd</t>
+  </si>
+  <si>
+    <t>Lengte van het kind bij aangegeven leeftijd</t>
+  </si>
+  <si>
+    <t>Heeft de moeder van het kind zwangerschapsdiabetes?</t>
+  </si>
+  <si>
+    <t>Nuchtere bloed glucose waarde van de moeder in het derde trimester</t>
+  </si>
+  <si>
+    <t>Family disease</t>
+  </si>
+  <si>
+    <t>Ziektegeschiedenis in de familie van de moeder</t>
   </si>
 </sst>
 </file>
@@ -793,21 +823,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -839,7 +869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -850,7 +880,7 @@
         <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
         <v>42</v>
@@ -865,7 +895,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -876,7 +906,7 @@
         <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
         <v>42</v>
@@ -891,7 +921,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -902,7 +932,7 @@
         <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
         <v>42</v>
@@ -917,7 +947,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -928,7 +958,7 @@
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
         <v>42</v>
@@ -943,7 +973,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -954,7 +984,7 @@
         <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
         <v>42</v>
@@ -969,7 +999,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -980,7 +1010,7 @@
         <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
         <v>42</v>
@@ -1002,31 +1032,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:U20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.06640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.1328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.19921875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.1328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1043,52 +1074,55 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>24</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>26</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>9</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>27</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>28</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>65</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1101,20 +1135,20 @@
       <c r="D2" t="s">
         <v>69</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>32</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>70</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>45</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1127,20 +1161,20 @@
       <c r="D3" t="s">
         <v>73</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>32</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>70</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>45</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1153,17 +1187,17 @@
       <c r="D4" t="s">
         <v>76</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>32</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>70</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -1180,19 +1214,22 @@
         <v>79</v>
       </c>
       <c r="F5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>80</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>49</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1209,16 +1246,19 @@
         <v>84</v>
       </c>
       <c r="F6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" t="s">
         <v>31</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>85</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1235,22 +1275,25 @@
         <v>88</v>
       </c>
       <c r="F7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" t="s">
         <v>31</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>85</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>89</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>90</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1267,22 +1310,25 @@
         <v>93</v>
       </c>
       <c r="F8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" t="s">
         <v>31</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>85</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>94</v>
       </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
         <v>95</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1299,22 +1345,25 @@
         <v>99</v>
       </c>
       <c r="F9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9" t="s">
         <v>36</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>85</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>89</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>90</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1331,22 +1380,25 @@
         <v>103</v>
       </c>
       <c r="F10" t="s">
+        <v>138</v>
+      </c>
+      <c r="G10" t="s">
         <v>36</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>85</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>94</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>95</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1363,19 +1415,22 @@
         <v>107</v>
       </c>
       <c r="F11" t="s">
+        <v>139</v>
+      </c>
+      <c r="G11" t="s">
         <v>35</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>108</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>109</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1392,22 +1447,25 @@
         <v>113</v>
       </c>
       <c r="F12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G12" t="s">
         <v>35</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>114</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>115</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>116</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1418,25 +1476,28 @@
         <v>117</v>
       </c>
       <c r="D13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" t="s">
         <v>118</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>142</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13" t="s">
         <v>119</v>
       </c>
-      <c r="F13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" t="s">
-        <v>80</v>
-      </c>
-      <c r="I13" t="s">
-        <v>45</v>
-      </c>
-      <c r="P13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1449,17 +1510,17 @@
       <c r="D14" t="s">
         <v>73</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>32</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>70</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1467,16 +1528,16 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
-      </c>
-      <c r="F15" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" t="s">
         <v>34</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1484,16 +1545,16 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16" t="s">
         <v>39</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1501,16 +1562,16 @@
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
-      </c>
-      <c r="F17" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" t="s">
         <v>38</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1518,16 +1579,16 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" t="s">
         <v>40</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1535,16 +1596,16 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
-      </c>
-      <c r="F19" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" t="s">
         <v>33</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1552,12 +1613,12 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" t="s">
         <v>130</v>
       </c>
-      <c r="F20" t="s">
-        <v>131</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1569,21 +1630,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.53125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1591,7 +1652,7 @@
         <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D1" t="s">
         <v>16</v>
@@ -1615,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1629,7 +1690,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
@@ -1641,7 +1702,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1655,7 +1716,7 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
@@ -1667,7 +1728,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1678,7 +1739,7 @@
         <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>

--- a/docs/resources/Dictionary_testCohort.xlsx
+++ b/docs/resources/Dictionary_testCohort.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C978146-3D7B-435B-9739-4D9C2F78E862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6506D6D-4A7F-4588-B52E-0BBC94E11502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Datasets" sheetId="9" r:id="rId1"/>
+    <sheet name="Tables" sheetId="9" r:id="rId1"/>
     <sheet name="Variables" sheetId="13" r:id="rId2"/>
     <sheet name="Variable values" sheetId="20" r:id="rId3"/>
   </sheets>
@@ -45,9 +45,6 @@
     <t>order</t>
   </si>
   <si>
-    <t>dataset type</t>
-  </si>
-  <si>
     <t>unit of observation</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>ontology term URI</t>
   </si>
   <si>
-    <t>dataset</t>
-  </si>
-  <si>
     <t>collection event</t>
   </si>
   <si>
@@ -222,9 +216,6 @@
     <t>useExternalDefinition.resource</t>
   </si>
   <si>
-    <t>useExternalDefinition.dataset</t>
-  </si>
-  <si>
     <t>useExternalDefinition.name</t>
   </si>
   <si>
@@ -451,6 +442,15 @@
   </si>
   <si>
     <t>Ziektegeschiedenis in de familie van de moeder</t>
+  </si>
+  <si>
+    <t>table type</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>useExternalDefinition.table</t>
   </si>
 </sst>
 </file>
@@ -848,181 +848,181 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
       </c>
       <c r="G1" t="s">
         <v>1</v>
       </c>
       <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>11</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>42</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>43</v>
-      </c>
-      <c r="H2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
       <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
         <v>46</v>
       </c>
-      <c r="D3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>47</v>
-      </c>
-      <c r="H3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" t="s">
         <v>50</v>
       </c>
-      <c r="C4" t="s">
+      <c r="H4" t="s">
         <v>51</v>
       </c>
-      <c r="D4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" t="s">
-        <v>53</v>
-      </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
         <v>54</v>
       </c>
-      <c r="C5" t="s">
+      <c r="H5" t="s">
         <v>55</v>
       </c>
-      <c r="D5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" t="s">
-        <v>57</v>
-      </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
         <v>58</v>
       </c>
-      <c r="C6" t="s">
+      <c r="H6" t="s">
         <v>59</v>
       </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" t="s">
-        <v>61</v>
-      </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
         <v>62</v>
       </c>
-      <c r="C7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>64</v>
-      </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
@@ -1074,552 +1074,552 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>24</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q1" t="s">
         <v>25</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>26</v>
       </c>
-      <c r="P1" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" t="s">
-        <v>28</v>
-      </c>
       <c r="S1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T1" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="U1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" t="s">
         <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="H5" t="s">
         <v>77</v>
       </c>
-      <c r="D5" t="s">
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="O5" t="s">
         <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>80</v>
-      </c>
-      <c r="J5" t="s">
-        <v>49</v>
-      </c>
-      <c r="O5" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
       <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
         <v>82</v>
       </c>
-      <c r="D6" t="s">
+      <c r="O6" t="s">
         <v>83</v>
-      </c>
-      <c r="E6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O6" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
       <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" t="s">
+        <v>86</v>
+      </c>
+      <c r="O7" t="s">
         <v>87</v>
       </c>
-      <c r="D7" t="s">
+      <c r="P7" t="s">
         <v>88</v>
-      </c>
-      <c r="E7" t="s">
-        <v>88</v>
-      </c>
-      <c r="F7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" t="s">
-        <v>85</v>
-      </c>
-      <c r="I7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O7" t="s">
-        <v>90</v>
-      </c>
-      <c r="P7" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
       <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" t="s">
+        <v>91</v>
+      </c>
+      <c r="O8" t="s">
         <v>92</v>
       </c>
-      <c r="D8" t="s">
+      <c r="P8" t="s">
         <v>93</v>
-      </c>
-      <c r="E8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F8" t="s">
-        <v>136</v>
-      </c>
-      <c r="G8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O8" t="s">
-        <v>95</v>
-      </c>
-      <c r="P8" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" t="s">
+        <v>86</v>
+      </c>
+      <c r="O9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P9" t="s">
         <v>97</v>
-      </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F9" t="s">
-        <v>137</v>
-      </c>
-      <c r="G9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" t="s">
-        <v>85</v>
-      </c>
-      <c r="I9" t="s">
-        <v>89</v>
-      </c>
-      <c r="O9" t="s">
-        <v>90</v>
-      </c>
-      <c r="P9" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" t="s">
+        <v>91</v>
+      </c>
+      <c r="O10" t="s">
+        <v>92</v>
+      </c>
+      <c r="P10" t="s">
         <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" t="s">
-        <v>138</v>
-      </c>
-      <c r="G10" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" t="s">
-        <v>94</v>
-      </c>
-      <c r="O10" t="s">
-        <v>95</v>
-      </c>
-      <c r="P10" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" t="s">
         <v>105</v>
       </c>
-      <c r="D11" t="s">
+      <c r="O11" t="s">
         <v>106</v>
       </c>
-      <c r="E11" t="s">
+      <c r="P11" t="s">
         <v>107</v>
-      </c>
-      <c r="F11" t="s">
-        <v>139</v>
-      </c>
-      <c r="G11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" t="s">
-        <v>108</v>
-      </c>
-      <c r="O11" t="s">
-        <v>109</v>
-      </c>
-      <c r="P11" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" t="s">
         <v>111</v>
       </c>
-      <c r="D12" t="s">
+      <c r="I12" t="s">
         <v>112</v>
       </c>
-      <c r="E12" t="s">
+      <c r="O12" t="s">
         <v>113</v>
       </c>
-      <c r="F12" t="s">
-        <v>140</v>
-      </c>
-      <c r="G12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" t="s">
-        <v>114</v>
-      </c>
-      <c r="I12" t="s">
-        <v>115</v>
-      </c>
-      <c r="O12" t="s">
-        <v>116</v>
-      </c>
       <c r="P12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1649,13 +1649,13 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="C1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -1664,94 +1664,94 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
       <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
         <v>11</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
         <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/resources/Dictionary_testCohort.xlsx
+++ b/docs/resources/Dictionary_testCohort.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6506D6D-4A7F-4588-B52E-0BBC94E11502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED3120A-4549-4754-9390-A5CE214B20E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="144">
   <si>
     <t>label</t>
   </si>
@@ -451,6 +451,9 @@
   </si>
   <si>
     <t>useExternalDefinition.table</t>
+  </si>
+  <si>
+    <t>http://snomed.info/id/118522005</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
@@ -1044,20 +1047,21 @@
     <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1086,43 +1090,46 @@
         <v>20</v>
       </c>
       <c r="J1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>22</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>23</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>24</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>25</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>26</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>63</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>142</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -1142,13 +1149,16 @@
         <v>67</v>
       </c>
       <c r="J2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K2" t="s">
         <v>43</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1167,14 +1177,14 @@
       <c r="H3" t="s">
         <v>67</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>43</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1193,11 +1203,11 @@
       <c r="H4" t="s">
         <v>67</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -1222,14 +1232,14 @@
       <c r="H5" t="s">
         <v>77</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>47</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1254,11 +1264,11 @@
       <c r="H6" t="s">
         <v>82</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1286,14 +1296,14 @@
       <c r="I7" t="s">
         <v>86</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>87</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1321,14 +1331,14 @@
       <c r="I8" t="s">
         <v>91</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>92</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1356,14 +1366,14 @@
       <c r="I9" t="s">
         <v>86</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>87</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1391,14 +1401,14 @@
       <c r="I10" t="s">
         <v>91</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>92</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1423,14 +1433,14 @@
       <c r="H11" t="s">
         <v>105</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>106</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1458,14 +1468,14 @@
       <c r="I12" t="s">
         <v>112</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>113</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -1490,14 +1500,14 @@
       <c r="H13" t="s">
         <v>77</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>43</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1516,11 +1526,11 @@
       <c r="H14" t="s">
         <v>67</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1533,11 +1543,11 @@
       <c r="G15" t="s">
         <v>32</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -1550,11 +1560,11 @@
       <c r="G16" t="s">
         <v>37</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -1567,11 +1577,11 @@
       <c r="G17" t="s">
         <v>36</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -1584,11 +1594,11 @@
       <c r="G18" t="s">
         <v>38</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1601,11 +1611,11 @@
       <c r="G19" t="s">
         <v>31</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1618,7 +1628,7 @@
       <c r="G20" t="s">
         <v>127</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>43</v>
       </c>
     </row>

--- a/docs/resources/Dictionary_testCohort.xlsx
+++ b/docs/resources/Dictionary_testCohort.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C978146-3D7B-435B-9739-4D9C2F78E862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEEDB47-3731-4A83-B4A1-32186D304196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="144">
   <si>
     <t>label</t>
   </si>
@@ -451,6 +451,9 @@
   </si>
   <si>
     <t>Ziektegeschiedenis in de familie van de moeder</t>
+  </si>
+  <si>
+    <t>http://snomed.info/id/118522005</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
@@ -1041,23 +1044,24 @@
     <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.109375" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.77734375" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1077,52 +1081,55 @@
         <v>132</v>
       </c>
       <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>24</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>25</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>26</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>27</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>28</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>65</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1136,19 +1143,22 @@
         <v>69</v>
       </c>
       <c r="G2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>70</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>45</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1161,20 +1171,20 @@
       <c r="D3" t="s">
         <v>73</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>70</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>45</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1187,17 +1197,17 @@
       <c r="D4" t="s">
         <v>76</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>70</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -1216,20 +1226,20 @@
       <c r="F5" t="s">
         <v>133</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>80</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>49</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1248,17 +1258,17 @@
       <c r="F6" t="s">
         <v>134</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>31</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>85</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1277,23 +1287,23 @@
       <c r="F7" t="s">
         <v>135</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>31</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>85</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>89</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>90</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1312,23 +1322,23 @@
       <c r="F8" t="s">
         <v>136</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>31</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>85</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>94</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>95</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1347,23 +1357,23 @@
       <c r="F9" t="s">
         <v>137</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>36</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>85</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>89</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>90</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1382,23 +1392,23 @@
       <c r="F10" t="s">
         <v>138</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>36</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>85</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>94</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>95</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1417,20 +1427,20 @@
       <c r="F11" t="s">
         <v>139</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>35</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>108</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>109</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1449,23 +1459,23 @@
       <c r="F12" t="s">
         <v>140</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>35</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>114</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>115</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>116</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1484,20 +1494,20 @@
       <c r="F13" t="s">
         <v>142</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>37</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>80</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>45</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1510,17 +1520,17 @@
       <c r="D14" t="s">
         <v>73</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>32</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>70</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1530,14 +1540,14 @@
       <c r="C15" t="s">
         <v>120</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>34</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1547,14 +1557,14 @@
       <c r="C16" t="s">
         <v>121</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>39</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1564,14 +1574,14 @@
       <c r="C17" t="s">
         <v>122</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>38</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1581,14 +1591,14 @@
       <c r="C18" t="s">
         <v>123</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>40</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1598,14 +1608,14 @@
       <c r="C19" t="s">
         <v>124</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>33</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1615,10 +1625,10 @@
       <c r="C20" t="s">
         <v>129</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>130</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>45</v>
       </c>
     </row>

--- a/docs/resources/Dictionary_testCohort.xlsx
+++ b/docs/resources/Dictionary_testCohort.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEEDB47-3731-4A83-B4A1-32186D304196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B406991-8311-49D0-88CD-1357CDDFB2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/docs/resources/Dictionary_testCohort.xlsx
+++ b/docs/resources/Dictionary_testCohort.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED3120A-4549-4754-9390-A5CE214B20E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E20DF1E-57B5-4C45-8507-F958381E2CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tables" sheetId="9" r:id="rId1"/>
-    <sheet name="Variables" sheetId="13" r:id="rId2"/>
+    <sheet name="Variables" sheetId="13" r:id="rId1"/>
+    <sheet name="Tables" sheetId="9" r:id="rId2"/>
     <sheet name="Variable values" sheetId="20" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -824,216 +824,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:V20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1637,6 +1427,216 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:J4"/>

--- a/docs/resources/Dictionary_testCohort.xlsx
+++ b/docs/resources/Dictionary_testCohort.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C978146-3D7B-435B-9739-4D9C2F78E862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B406991-8311-49D0-88CD-1357CDDFB2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="144">
   <si>
     <t>label</t>
   </si>
@@ -451,6 +451,9 @@
   </si>
   <si>
     <t>Ziektegeschiedenis in de familie van de moeder</t>
+  </si>
+  <si>
+    <t>http://snomed.info/id/118522005</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
@@ -1041,23 +1044,24 @@
     <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.109375" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.77734375" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1077,52 +1081,55 @@
         <v>132</v>
       </c>
       <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>24</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>25</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>26</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>27</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>28</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>65</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1136,19 +1143,22 @@
         <v>69</v>
       </c>
       <c r="G2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>70</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>45</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1161,20 +1171,20 @@
       <c r="D3" t="s">
         <v>73</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>70</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>45</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1187,17 +1197,17 @@
       <c r="D4" t="s">
         <v>76</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>70</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -1216,20 +1226,20 @@
       <c r="F5" t="s">
         <v>133</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>80</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>49</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1248,17 +1258,17 @@
       <c r="F6" t="s">
         <v>134</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>31</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>85</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1277,23 +1287,23 @@
       <c r="F7" t="s">
         <v>135</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>31</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>85</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>89</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>90</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1312,23 +1322,23 @@
       <c r="F8" t="s">
         <v>136</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>31</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>85</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>94</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>95</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1347,23 +1357,23 @@
       <c r="F9" t="s">
         <v>137</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>36</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>85</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>89</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>90</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1382,23 +1392,23 @@
       <c r="F10" t="s">
         <v>138</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>36</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>85</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>94</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>95</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1417,20 +1427,20 @@
       <c r="F11" t="s">
         <v>139</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>35</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>108</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>109</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1449,23 +1459,23 @@
       <c r="F12" t="s">
         <v>140</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>35</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>114</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>115</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>116</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1484,20 +1494,20 @@
       <c r="F13" t="s">
         <v>142</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>37</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>80</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>45</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1510,17 +1520,17 @@
       <c r="D14" t="s">
         <v>73</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>32</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>70</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1530,14 +1540,14 @@
       <c r="C15" t="s">
         <v>120</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>34</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1547,14 +1557,14 @@
       <c r="C16" t="s">
         <v>121</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>39</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1564,14 +1574,14 @@
       <c r="C17" t="s">
         <v>122</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>38</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1581,14 +1591,14 @@
       <c r="C18" t="s">
         <v>123</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>40</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1598,14 +1608,14 @@
       <c r="C19" t="s">
         <v>124</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>33</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1615,10 +1625,10 @@
       <c r="C20" t="s">
         <v>129</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>130</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>45</v>
       </c>
     </row>

--- a/docs/resources/Dictionary_testCohort.xlsx
+++ b/docs/resources/Dictionary_testCohort.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B406991-8311-49D0-88CD-1357CDDFB2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E20DF1E-57B5-4C45-8507-F958381E2CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Datasets" sheetId="9" r:id="rId1"/>
-    <sheet name="Variables" sheetId="13" r:id="rId2"/>
+    <sheet name="Variables" sheetId="13" r:id="rId1"/>
+    <sheet name="Tables" sheetId="9" r:id="rId2"/>
     <sheet name="Variable values" sheetId="20" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -45,9 +45,6 @@
     <t>order</t>
   </si>
   <si>
-    <t>dataset type</t>
-  </si>
-  <si>
     <t>unit of observation</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>ontology term URI</t>
   </si>
   <si>
-    <t>dataset</t>
-  </si>
-  <si>
     <t>collection event</t>
   </si>
   <si>
@@ -222,9 +216,6 @@
     <t>useExternalDefinition.resource</t>
   </si>
   <si>
-    <t>useExternalDefinition.dataset</t>
-  </si>
-  <si>
     <t>useExternalDefinition.name</t>
   </si>
   <si>
@@ -451,6 +442,15 @@
   </si>
   <si>
     <t>Ziektegeschiedenis in de familie van de moeder</t>
+  </si>
+  <si>
+    <t>table type</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>useExternalDefinition.table</t>
   </si>
   <si>
     <t>http://snomed.info/id/118522005</t>
@@ -824,6 +824,610 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:V20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1" t="s">
+        <v>142</v>
+      </c>
+      <c r="V1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="P5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>82</v>
+      </c>
+      <c r="P6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" t="s">
+        <v>86</v>
+      </c>
+      <c r="P7" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" t="s">
+        <v>91</v>
+      </c>
+      <c r="P8" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" t="s">
+        <v>91</v>
+      </c>
+      <c r="P10" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" t="s">
+        <v>105</v>
+      </c>
+      <c r="P11" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" t="s">
+        <v>111</v>
+      </c>
+      <c r="I12" t="s">
+        <v>112</v>
+      </c>
+      <c r="P12" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" t="s">
+        <v>43</v>
+      </c>
+      <c r="R13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
+        <v>126</v>
+      </c>
+      <c r="G20" t="s">
+        <v>127</v>
+      </c>
+      <c r="K20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -851,785 +1455,181 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
       </c>
       <c r="G1" t="s">
         <v>1</v>
       </c>
       <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>11</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>42</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>43</v>
-      </c>
-      <c r="H2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
       <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
         <v>46</v>
       </c>
-      <c r="D3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>47</v>
-      </c>
-      <c r="H3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" t="s">
         <v>50</v>
       </c>
-      <c r="C4" t="s">
+      <c r="H4" t="s">
         <v>51</v>
       </c>
-      <c r="D4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" t="s">
-        <v>53</v>
-      </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
         <v>54</v>
       </c>
-      <c r="C5" t="s">
+      <c r="H5" t="s">
         <v>55</v>
       </c>
-      <c r="D5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" t="s">
-        <v>57</v>
-      </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
         <v>58</v>
       </c>
-      <c r="C6" t="s">
+      <c r="H6" t="s">
         <v>59</v>
       </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" t="s">
-        <v>61</v>
-      </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
         <v>62</v>
       </c>
-      <c r="C7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>64</v>
-      </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:V20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.109375" customWidth="1"/>
-    <col min="7" max="7" width="26.77734375" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" t="s">
-        <v>28</v>
-      </c>
-      <c r="T1" t="s">
-        <v>65</v>
-      </c>
-      <c r="U1" t="s">
-        <v>66</v>
-      </c>
-      <c r="V1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" t="s">
-        <v>80</v>
-      </c>
-      <c r="K5" t="s">
-        <v>49</v>
-      </c>
-      <c r="P5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" t="s">
-        <v>134</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" t="s">
-        <v>85</v>
-      </c>
-      <c r="P6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" t="s">
-        <v>88</v>
-      </c>
-      <c r="F7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J7" t="s">
-        <v>89</v>
-      </c>
-      <c r="P7" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F8" t="s">
-        <v>136</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" t="s">
-        <v>85</v>
-      </c>
-      <c r="J8" t="s">
-        <v>94</v>
-      </c>
-      <c r="P8" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F9" t="s">
-        <v>137</v>
-      </c>
-      <c r="H9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" t="s">
-        <v>85</v>
-      </c>
-      <c r="J9" t="s">
-        <v>89</v>
-      </c>
-      <c r="P9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" t="s">
-        <v>138</v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" t="s">
-        <v>85</v>
-      </c>
-      <c r="J10" t="s">
-        <v>94</v>
-      </c>
-      <c r="P10" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" t="s">
-        <v>139</v>
-      </c>
-      <c r="H11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" t="s">
-        <v>108</v>
-      </c>
-      <c r="P11" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" t="s">
-        <v>140</v>
-      </c>
-      <c r="H12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J12" t="s">
-        <v>115</v>
-      </c>
-      <c r="P12" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F13" t="s">
-        <v>142</v>
-      </c>
-      <c r="H13" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" t="s">
-        <v>80</v>
-      </c>
-      <c r="K13" t="s">
-        <v>45</v>
-      </c>
-      <c r="R13" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" t="s">
-        <v>120</v>
-      </c>
-      <c r="H15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
-        <v>121</v>
-      </c>
-      <c r="H16" t="s">
-        <v>39</v>
-      </c>
-      <c r="K16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" t="s">
-        <v>122</v>
-      </c>
-      <c r="H17" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" t="s">
-        <v>123</v>
-      </c>
-      <c r="H18" t="s">
-        <v>40</v>
-      </c>
-      <c r="K18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" t="s">
-        <v>124</v>
-      </c>
-      <c r="H19" t="s">
-        <v>33</v>
-      </c>
-      <c r="K19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" t="s">
-        <v>129</v>
-      </c>
-      <c r="H20" t="s">
-        <v>130</v>
-      </c>
-      <c r="K20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1659,13 +1659,13 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="C1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -1674,94 +1674,94 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
       <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
         <v>11</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
         <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
